--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -1136,53 +1136,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B6" t="n">
-        <v>56926</v>
+        <v>80186</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R6" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,6 +1228,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,51 +1247,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>56926</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R7" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -1136,51 +1136,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>56926</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R6" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1247,53 +1253,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B7" t="n">
-        <v>56926</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R7" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129822109</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129813860</v>
       </c>
       <c r="B3" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129822067</v>
       </c>
       <c r="B4" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129812807</v>
       </c>
       <c r="B5" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1139,7 +1139,7 @@
         <v>129822064</v>
       </c>
       <c r="B6" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1250,7 +1250,7 @@
         <v>129822172</v>
       </c>
       <c r="B7" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -1136,51 +1136,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B6" t="n">
-        <v>80189</v>
+        <v>56927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R6" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1247,53 +1253,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B7" t="n">
-        <v>56927</v>
+        <v>80189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R7" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129822109</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129813860</v>
       </c>
       <c r="B3" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -906,7 +906,7 @@
         <v>129822067</v>
       </c>
       <c r="B4" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129812807</v>
       </c>
       <c r="B5" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,53 +1136,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B6" t="n">
-        <v>56927</v>
+        <v>80192</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R6" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,6 +1228,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,51 +1247,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B7" t="n">
-        <v>80189</v>
+        <v>56930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R7" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129822109</v>
       </c>
       <c r="B2" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129813860</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129822067</v>
       </c>
       <c r="B4" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>129822064</v>
       </c>
       <c r="B6" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -1136,51 +1136,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B6" t="n">
-        <v>80193</v>
+        <v>56930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R6" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,7 +1211,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1221,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1228,7 +1235,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1247,53 +1253,51 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B7" t="n">
-        <v>56930</v>
+        <v>80193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R7" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1322,7 +1326,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1332,12 +1336,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,6 +1345,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129822109</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129813860</v>
       </c>
       <c r="B3" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129822067</v>
       </c>
       <c r="B4" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1136,53 +1136,51 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822172</v>
+        <v>129822064</v>
       </c>
       <c r="B6" t="n">
-        <v>56930</v>
+        <v>80194</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473130</v>
+        <v>473200</v>
       </c>
       <c r="R6" t="n">
-        <v>6801485</v>
+        <v>6801472</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:53</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1221,12 +1219,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:53</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,6 +1228,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1253,51 +1247,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822064</v>
+        <v>129822172</v>
       </c>
       <c r="B7" t="n">
-        <v>80193</v>
+        <v>56930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473200</v>
+        <v>473130</v>
       </c>
       <c r="R7" t="n">
-        <v>6801472</v>
+        <v>6801485</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1326,7 +1322,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1332,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1346,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -896,7 +896,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Peter Turander, Birgitta Kvist, Bengt Oldhammer</t>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129822109</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>129813860</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>129822067</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>129812807</v>
       </c>
       <c r="B5" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>129822172</v>
       </c>
       <c r="B6" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
         <v>129822064</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129822109</v>
+        <v>129822067</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>473184</v>
+        <v>473200</v>
       </c>
       <c r="R2" t="n">
-        <v>6801494</v>
+        <v>6801472</v>
       </c>
       <c r="S2" t="n">
         <v>8</v>
@@ -782,57 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129813860</v>
+        <v>129822109</v>
       </c>
       <c r="B3" t="n">
-        <v>80200</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>473174</v>
+        <v>473184</v>
       </c>
       <c r="R3" t="n">
-        <v>6801524</v>
+        <v>6801494</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:41</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Nyetablering</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129822067</v>
+        <v>129813860</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,37 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>473200</v>
+        <v>473174</v>
       </c>
       <c r="R4" t="n">
-        <v>6801472</v>
+        <v>6801524</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -973,7 +968,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -983,7 +978,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:41</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Nyetablering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,64 +1010,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129812807</v>
+        <v>129822064</v>
       </c>
       <c r="B5" t="n">
-        <v>56931</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>473142</v>
+        <v>473200</v>
       </c>
       <c r="R5" t="n">
-        <v>6801527</v>
+        <v>6801472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,7 +1083,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,7 +1093,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1118,6 +1102,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1136,53 +1121,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129822172</v>
+        <v>129838245</v>
       </c>
       <c r="B6" t="n">
-        <v>56931</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gangsberget, Gangsberget, Dlr</t>
+          <t>Skrattabborrtjärnen, Skrattabborrtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>473130</v>
+        <v>472871</v>
       </c>
       <c r="R6" t="n">
-        <v>6801485</v>
+        <v>6801463</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1209,24 +1194,14 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>12:53</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Flera tjäderbetade tallar</t>
+          <t>Ringhackad tall. Precis utanför området som ska avverkas</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1253,48 +1228,64 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129822064</v>
+        <v>129812807</v>
       </c>
       <c r="B7" t="n">
-        <v>80200</v>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gangsberget, Gangsberget, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>473200</v>
+        <v>473142</v>
       </c>
       <c r="R7" t="n">
-        <v>6801472</v>
+        <v>6801527</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1326,7 +1317,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1336,7 +1327,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1336,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1361,6 +1351,123 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129822172</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gangsberget, Gangsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>473130</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6801485</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:53</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Flera tjäderbetade tallar</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Bengt Oldhammer, Birgitta Kvist, Peter Turander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51070-2025 artfynd.xlsx
+++ b/artfynd/A 51070-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822109</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129813860</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1118,6 +1138,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822064</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1225,6 +1250,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129838245</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129812807</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1468,8 +1503,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129822172</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>